--- a/res/prototype-v1-采购清单.xlsx
+++ b/res/prototype-v1-采购清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\starling\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C152FC31-DE0E-484A-A92C-AA9A1C39FAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80605E03-3510-49E8-8EEA-07BE08F02A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="241">
   <si>
     <t>序号</t>
   </si>
@@ -481,7 +481,7 @@
     <t>PETG 耗材 1kg</t>
   </si>
   <si>
-    <t>PETG 耐热日晒;已有 PLA 可先跑台架</t>
+    <t>★2026-07-02 路线变更:打印全走农场代打 PA12/PA12-CF(见 cad/dist),自有耗材仅备用;原 PLA→PETG 路线作废</t>
   </si>
   <si>
     <t>工具辅材</t>
@@ -551,6 +551,21 @@
   </si>
   <si>
     <t>取 SD 日志</t>
+  </si>
+  <si>
+    <t>环氧 AB 胶</t>
+  </si>
+  <si>
+    <t>5 分钟固化型(哥俩好/爱牢达)</t>
+  </si>
+  <si>
+    <t>支</t>
+  </si>
+  <si>
+    <t>环氧AB胶 5分钟</t>
+  </si>
+  <si>
+    <t>★PA12 尼龙粘不住 502/CA:钢轴入叶槽、曲柄固轴端一律用环氧,粘接面砂纸打毛</t>
   </si>
   <si>
     <t>合计(全部)</t>
@@ -749,7 +764,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -807,6 +822,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -848,7 +878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -887,6 +917,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1191,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1207,7 +1243,7 @@
     <col min="11" max="11" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6">
+    <row r="1" spans="1:11" ht="15.6" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1242,7 +1278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30">
+    <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1265,7 +1301,7 @@
         <v>25</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H38" si="0">E2*G2</f>
+        <f t="shared" ref="H2:H39" si="0">E2*G2</f>
         <v>50</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -1278,7 +1314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30">
+    <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1314,7 +1350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30">
+    <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1350,7 +1386,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30">
+    <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1386,7 +1422,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30">
+    <row r="6" spans="1:11" ht="30" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1422,7 +1458,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30">
+    <row r="7" spans="1:11" ht="30" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1458,7 +1494,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="30">
+    <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1494,7 +1530,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="30">
+    <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1530,7 +1566,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.6">
+    <row r="10" spans="1:11" ht="15.6" customHeight="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1566,7 +1602,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="30">
+    <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1602,7 +1638,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30">
+    <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1638,7 +1674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="30">
+    <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1674,7 +1710,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.6">
+    <row r="14" spans="1:11" ht="15.6" customHeight="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1710,7 +1746,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="30">
+    <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1746,7 +1782,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15">
+    <row r="16" spans="1:11" ht="15" customHeight="1">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1782,7 +1818,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15">
+    <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1818,7 +1854,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.6">
+    <row r="18" spans="1:11" ht="15.6" customHeight="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1854,7 +1890,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.6">
+    <row r="19" spans="1:11" ht="15.6" customHeight="1">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1890,7 +1926,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.6">
+    <row r="20" spans="1:11" ht="15.6" customHeight="1">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1926,7 +1962,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.6">
+    <row r="21" spans="1:11" ht="15.6" customHeight="1">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1962,7 +1998,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.6">
+    <row r="22" spans="1:11" ht="15.6" customHeight="1">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1998,7 +2034,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.6">
+    <row r="23" spans="1:11" ht="15.6" customHeight="1">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2032,7 +2068,7 @@
       </c>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="15">
+    <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2068,7 +2104,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.6">
+    <row r="25" spans="1:11" ht="15.6" customHeight="1">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2104,7 +2140,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.6">
+    <row r="26" spans="1:11" ht="15.6" customHeight="1">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2140,7 +2176,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.6">
+    <row r="27" spans="1:11" ht="15.6" customHeight="1">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2176,7 +2212,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.6">
+    <row r="28" spans="1:11" ht="15.6" customHeight="1">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2212,7 +2248,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="30">
+    <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2248,7 +2284,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.6">
+    <row r="30" spans="1:11" ht="15.6" customHeight="1">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2284,7 +2320,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.6">
+    <row r="31" spans="1:11" ht="15.6" customHeight="1">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2320,7 +2356,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15">
+    <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2350,13 +2386,13 @@
         <v>147</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.6">
+    <row r="33" spans="1:11" ht="15.6" customHeight="1">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2392,7 +2428,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15">
+    <row r="34" spans="1:11" ht="15" customHeight="1">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2428,7 +2464,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15">
+    <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2464,7 +2500,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15">
+    <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2498,7 +2534,7 @@
       </c>
       <c r="K36" s="3"/>
     </row>
-    <row r="37" spans="1:11" ht="15.6">
+    <row r="37" spans="1:11" ht="15.6" customHeight="1">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2534,7 +2570,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15">
+    <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2570,111 +2606,132 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="9"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.6">
+    <row r="39" spans="1:11" ht="15" customHeight="1">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G39" s="4">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.6" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="11" t="s">
-        <v>172</v>
-      </c>
+      <c r="D40" s="9"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="10"/>
-      <c r="H40" s="12">
-        <f>SUM(H2:H38)</f>
-        <v>826</v>
-      </c>
+      <c r="H40" s="10"/>
       <c r="I40" s="9"/>
       <c r="J40" s="8"/>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" ht="15.6">
+    <row r="41" spans="1:11" ht="15.6" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="10"/>
       <c r="H41" s="12">
-        <f>SUMIF(J2:J38,"必买",H2:H38)</f>
-        <v>615</v>
+        <f>SUM(H2:H39)</f>
+        <v>836</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="8"/>
       <c r="K41" s="9"/>
     </row>
-    <row r="42" spans="1:11" ht="15.6">
+    <row r="42" spans="1:11" ht="15.6" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="10"/>
       <c r="H42" s="12">
-        <f>SUMIF(J2:J38,"已有可跳过",H2:H38)</f>
-        <v>201</v>
+        <f>SUMIF(J2:J39,"必买",H2:H39)</f>
+        <v>625</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="8"/>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="15.6">
+    <row r="43" spans="1:11" ht="15.6" customHeight="1">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="10"/>
       <c r="H43" s="12">
-        <f>SUMIF(J2:J38,"可选",H2:H38)</f>
-        <v>10</v>
+        <f>SUMIF(J2:J39,"已有可跳过",H2:H39)</f>
+        <v>146</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8"/>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" spans="1:11" ht="15">
+    <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
+      <c r="D44" s="11" t="s">
+        <v>180</v>
+      </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="H44" s="12">
+        <f>SUMIF(J2:J39,"可选",H2:H39)</f>
+        <v>65</v>
+      </c>
       <c r="I44" s="9"/>
       <c r="J44" s="8"/>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11" ht="30">
+    <row r="45" spans="1:11" ht="30" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="9" t="s">
-        <v>176</v>
-      </c>
+      <c r="D45" s="9"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="10"/>
@@ -2682,6 +2739,21 @@
       <c r="I45" s="9"/>
       <c r="J45" s="8"/>
       <c r="K45" s="9"/>
+    </row>
+    <row r="46" spans="1:11" ht="30">
+      <c r="A46" s="8"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2704,7 +2776,7 @@
     <col min="8" max="8" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6">
+    <row r="1" spans="1:8" ht="15.6" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2727,10 +2799,10 @@
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2738,10 +2810,10 @@
         <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -2754,10 +2826,10 @@
         <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2765,10 +2837,10 @@
         <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
@@ -2781,10 +2853,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2792,10 +2864,10 @@
         <v>62</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -2808,21 +2880,21 @@
         <v>6</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -2835,21 +2907,21 @@
         <v>15</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -2862,21 +2934,21 @@
         <v>12</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2889,21 +2961,21 @@
         <v>120</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -2916,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -2929,12 +3001,12 @@
       <c r="G9" s="10"/>
       <c r="H9" s="9"/>
     </row>
-    <row r="10" spans="1:8" ht="15.6">
+    <row r="10" spans="1:8" ht="15.6" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="10"/>
@@ -2959,140 +3031,140 @@
     <col min="2" max="2" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6">
+    <row r="1" spans="1:2" ht="15.6" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.6">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.6">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.6" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.6">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.6" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.6" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.6" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
     </row>
-    <row r="13" spans="1:2" ht="15.6">
+    <row r="13" spans="1:2" ht="15.6" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="31.2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="31.2" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.6">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.6" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
     </row>
-    <row r="18" spans="1:2" ht="15.6">
+    <row r="18" spans="1:2" ht="15.6" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
